--- a/media/templates/APS排产信息模板.xlsx
+++ b/media/templates/APS排产信息模板.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\药业代码\片剂药物智能排程系统算法\药业\输入\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\片剂药物智能排程系统\交互说明及模板文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="APS生产信息统计" sheetId="5" r:id="rId1"/>
@@ -160,7 +160,7 @@
     <t>100mg×15片×2板×400盒</t>
   </si>
   <si>
-    <t>注：当前展示的是示例数据，可删除后上传您的数据。</t>
+    <t>注：当前展示的是示例数据，可删除后上传您的数据，上传时请删除该行信息避免影响您的使用。</t>
   </si>
 </sst>
 </file>
@@ -173,7 +173,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +204,14 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -748,137 +756,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -911,6 +919,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1261,19 +1272,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="23.5272727272727" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.525" style="1" customWidth="1"/>
     <col min="2" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1833333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="2" customWidth="1"/>
     <col min="5" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1818181818182" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1833333333333" style="1" customWidth="1"/>
     <col min="8" max="15" width="9" style="1" customWidth="1"/>
     <col min="16" max="19" width="9" style="1"/>
-    <col min="20" max="20" width="12.9090909090909" style="1" customWidth="1"/>
-    <col min="21" max="21" width="15.1818181818182" style="1" customWidth="1"/>
-    <col min="22" max="22" width="13.3636363636364" style="1" customWidth="1"/>
+    <col min="20" max="20" width="12.9083333333333" style="1" customWidth="1"/>
+    <col min="21" max="21" width="15.1833333333333" style="1" customWidth="1"/>
+    <col min="22" max="22" width="13.3666666666667" style="1" customWidth="1"/>
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1321,7 +1332,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="39" spans="1:22">
+    <row r="2" ht="36" spans="1:22">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
@@ -1583,7 +1594,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:22">
+    <row r="6" ht="25.5" spans="1:22">
       <c r="A6" s="9" t="s">
         <v>19</v>
       </c>
@@ -1651,7 +1662,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:22">
+    <row r="7" ht="25.5" spans="1:22">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
@@ -1719,7 +1730,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:22">
+    <row r="8" ht="25.5" spans="1:22">
       <c r="A8" s="9" t="s">
         <v>19</v>
       </c>
@@ -1787,7 +1798,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:22">
+    <row r="9" ht="25.5" spans="1:22">
       <c r="A9" s="9" t="s">
         <v>19</v>
       </c>
@@ -1855,7 +1866,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="10" ht="27" spans="1:22">
+    <row r="10" ht="25.5" spans="1:22">
       <c r="A10" s="9" t="s">
         <v>19</v>
       </c>
@@ -1923,7 +1934,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="11" ht="27" spans="1:22">
+    <row r="11" ht="25.5" spans="1:22">
       <c r="A11" s="9" t="s">
         <v>19</v>
       </c>
@@ -1991,7 +2002,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:22">
+    <row r="12" ht="25.5" spans="1:22">
       <c r="A12" s="9" t="s">
         <v>19</v>
       </c>
@@ -2059,7 +2070,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="13" ht="27" spans="1:22">
+    <row r="13" ht="25.5" spans="1:22">
       <c r="A13" s="9" t="s">
         <v>19</v>
       </c>
@@ -2195,7 +2206,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="15" ht="27" spans="1:22">
+    <row r="15" ht="25.5" spans="1:22">
       <c r="A15" s="9" t="s">
         <v>19</v>
       </c>
@@ -2263,7 +2274,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="16" ht="27" spans="1:22">
+    <row r="16" ht="25.5" spans="1:22">
       <c r="A16" s="9" t="s">
         <v>19</v>
       </c>
@@ -2331,8 +2342,9 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:2">
-      <c r="B18" s="10" t="s">
+    <row r="18" ht="18.75" spans="2:4">
+      <c r="B18" s="10"/>
+      <c r="D18" s="11" t="s">
         <v>42</v>
       </c>
     </row>
